--- a/SQLQry2T.xlsx
+++ b/SQLQry2T.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13261FD-3453-4C58-9FE2-A798BA99F732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358B08EC-942C-44AE-9AD1-C46FC2397F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1AFE925-2940-40C5-94CE-9E207745A12B}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Site Code Deployment</t>
   </si>
   <si>
-    <t>Geographic Region Node</t>
-  </si>
-  <si>
     <t>Active Store Footprint Count</t>
   </si>
   <si>
@@ -98,6 +95,9 @@
   </si>
   <si>
     <t>BYD-CHN-08</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -998,7 +998,7 @@
     <tableColumn id="1" xr3:uid="{44535F99-84BA-45E1-B4B4-C411050BE375}" name="Retail Fuel Brand" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{6C9AA7F4-D592-47F5-9387-5109FDAC8CC1}" name="Operational Theater" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{790B09A8-8709-48E4-A4E6-F92409CBB90F}" name="Site Code Deployment" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{A93995C9-FF88-4D76-B9B3-62318541B713}" name="Geographic Region Node" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{A93995C9-FF88-4D76-B9B3-62318541B713}" name="Region" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{4FA6FB5D-6084-4FD2-A4EA-962E334ABA36}" name="Active Store Footprint Count" dataDxfId="5"/>
     <tableColumn id="6" xr3:uid="{D203EA0B-511F-4F15-A57B-0EC245FE9124}" name="Active Tracking Inventory Units" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{5099C5D0-6812-4D20-925A-A94AA4410990}" name="Average Unit Cost (MSRP)" dataDxfId="3"/>
@@ -1353,25 +1353,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>9</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1388,16 +1388,16 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="1">
         <v>12</v>
@@ -1415,7 +1415,7 @@
         <v>191400000</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1432,16 +1432,16 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="1">
         <v>12</v>
@@ -1459,7 +1459,7 @@
         <v>191400000</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1476,16 +1476,16 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
         <v>34</v>
@@ -1503,7 +1503,7 @@
         <v>176900000</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1520,16 +1520,16 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1">
         <v>34</v>
@@ -1547,7 +1547,7 @@
         <v>176900000</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1564,16 +1564,16 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>19</v>
@@ -1591,7 +1591,7 @@
         <v>171100000</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1608,16 +1608,16 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1">
         <v>19</v>
@@ -1635,7 +1635,7 @@
         <v>171100000</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1652,16 +1652,16 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1">
         <v>45</v>
@@ -1679,7 +1679,7 @@
         <v>166750000</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1696,16 +1696,16 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>45</v>
@@ -1723,7 +1723,7 @@
         <v>166750000</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1740,16 +1740,16 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1">
         <v>88</v>
@@ -1767,7 +1767,7 @@
         <v>153700000</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1784,16 +1784,16 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>25</v>
-      </c>
       <c r="D11" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="10">
         <v>88</v>
@@ -1811,7 +1811,7 @@
         <v>153700000</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>

--- a/SQLQry2T.xlsx
+++ b/SQLQry2T.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358B08EC-942C-44AE-9AD1-C46FC2397F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BB87F3-35C3-46B1-BE80-72C949C92433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1AFE925-2940-40C5-94CE-9E207745A12B}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
   <si>
-    <t>Retail Fuel Brand</t>
-  </si>
-  <si>
     <t>Operational Theater</t>
   </si>
   <si>
@@ -98,6 +95,9 @@
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>Command Tier</t>
   </si>
 </sst>
 </file>
@@ -995,7 +995,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9147E719-4CE0-4334-8CDB-212916EBD0D6}" name="Table1" displayName="Table1" ref="A1:J11" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:J11" xr:uid="{9147E719-4CE0-4334-8CDB-212916EBD0D6}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{44535F99-84BA-45E1-B4B4-C411050BE375}" name="Retail Fuel Brand" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{44535F99-84BA-45E1-B4B4-C411050BE375}" name="Command Tier" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{6C9AA7F4-D592-47F5-9387-5109FDAC8CC1}" name="Operational Theater" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{790B09A8-8709-48E4-A4E6-F92409CBB90F}" name="Site Code Deployment" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{A93995C9-FF88-4D76-B9B3-62318541B713}" name="Region" dataDxfId="6"/>
@@ -1344,34 +1344,34 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>8</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1388,16 +1388,16 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="1">
         <v>12</v>
@@ -1415,7 +1415,7 @@
         <v>191400000</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1432,16 +1432,16 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E3" s="1">
         <v>12</v>
@@ -1459,7 +1459,7 @@
         <v>191400000</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1476,16 +1476,16 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1">
         <v>34</v>
@@ -1503,7 +1503,7 @@
         <v>176900000</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1520,16 +1520,16 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1">
         <v>34</v>
@@ -1547,7 +1547,7 @@
         <v>176900000</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1564,16 +1564,16 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1">
         <v>19</v>
@@ -1591,7 +1591,7 @@
         <v>171100000</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1608,16 +1608,16 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1">
         <v>19</v>
@@ -1635,7 +1635,7 @@
         <v>171100000</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1652,16 +1652,16 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
         <v>45</v>
@@ -1679,7 +1679,7 @@
         <v>166750000</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1696,16 +1696,16 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1">
         <v>45</v>
@@ -1723,7 +1723,7 @@
         <v>166750000</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1740,16 +1740,16 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1">
         <v>88</v>
@@ -1767,7 +1767,7 @@
         <v>153700000</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1784,16 +1784,16 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>24</v>
-      </c>
       <c r="D11" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" s="10">
         <v>88</v>
@@ -1811,7 +1811,7 @@
         <v>153700000</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
